--- a/tests/worked_examples/_template.xlsx
+++ b/tests/worked_examples/_template.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">Template for a new worked example. Copy this file, rename it, and replace the metadata, inputs and expected rows. Keep the three section markers in column A, name every value cell in column B (select columns A and B, then Formulas &gt; Create from Selection), write expected values as formulas over those names, and leave the three review rows empty until a human has re-derived the sheet.</t>
+    <t xml:space="preserve">Template for a new worked example. Copy this file, rename it, and replace the metadata, inputs and expected rows. The metadata name must equal the new file stem (validation rule 9). Keep the three section markers in column A, name every value cell in column B (select columns A and B, then Formulas &gt; Create from Selection), write expected values as formulas over those names, leave the value and tolerance cells formatted General (rule 10 - Excel's PMT wizard leaves a dollar format behind), and leave the three review rows empty until a human has re-derived the sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">reviewed_by</t>
@@ -199,12 +199,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -411,171 +415,171 @@
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <f aca="false">principal_in_euro*interest_rate*(1+interest_rate)^duration_in_years/((1+interest_rate)^duration_in_years-1)</f>
         <v>2344.61013210319</v>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <f aca="false">principal_in_euro*interest_rate</f>
         <v>600</v>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>29</v>
       </c>
     </row>
